--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.63092297987372</v>
+        <v>3.190024984229479</v>
       </c>
       <c r="D2" t="n">
-        <v>19.07342742392589</v>
+        <v>3.099431956387958</v>
       </c>
       <c r="E2" t="n">
-        <v>18.54806493506425</v>
+        <v>3.014060551947941</v>
       </c>
       <c r="F2" t="n">
-        <v>17.56204900639155</v>
+        <v>2.853832963538627</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.96261823259953</v>
+        <v>6.006425462797425</v>
       </c>
       <c r="D3" t="n">
-        <v>21.36109023822218</v>
+        <v>3.471177163711105</v>
       </c>
       <c r="E3" t="n">
-        <v>18.54806493506425</v>
+        <v>3.014060551947941</v>
       </c>
       <c r="F3" t="n">
-        <v>17.56204900639155</v>
+        <v>2.853832963538627</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.66774065803895</v>
+        <v>10.50850785693133</v>
       </c>
       <c r="D4" t="n">
-        <v>57.41927481138225</v>
+        <v>9.330632156849616</v>
       </c>
       <c r="E4" t="n">
-        <v>18.54806493506425</v>
+        <v>3.014060551947941</v>
       </c>
       <c r="F4" t="n">
-        <v>17.56204900639155</v>
+        <v>2.853832963538627</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
